--- a/originales/respuestas/2025/01. Calificadas/bucle p15/Secretaría General De La Alcaldía Mayor De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p15/Secretaría General De La Alcaldía Mayor De Bogotá.xlsx
@@ -464,7 +464,7 @@
     <col customWidth="1" min="3" max="3" width="24.71"/>
     <col customWidth="1" min="4" max="4" width="24.14"/>
     <col customWidth="1" min="5" max="5" width="10.71"/>
-    <col customWidth="1" min="6" max="6" width="32.0"/>
+    <col customWidth="1" min="6" max="6" width="66.29"/>
     <col customWidth="1" min="7" max="26" width="10.71"/>
   </cols>
   <sheetData>
